--- a/sample_data/it_presentation.xlsx
+++ b/sample_data/it_presentation.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -636,12 +636,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>t3_2</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prof. Sneha Joshi</t>
+          <t>Prof. Aniket Joshi</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -654,16 +654,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>faculty32@example.edu</t>
+          <t>lab31@example.edu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>F32</t>
+          <t>L31</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -682,12 +682,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>t3_3</t>
+          <t>t3_2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prof. Amit Shah</t>
+          <t>Prof. Sneha Joshi</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -700,12 +700,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>faculty33@example.edu</t>
+          <t>faculty32@example.edu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>F33</t>
+          <t>F32</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -728,12 +728,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>t3_4</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prof. Pooja Kulkarni</t>
+          <t>Prof. Riya Kulkarni</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -746,16 +746,16 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>faculty34@example.edu</t>
+          <t>lab32@example.edu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>F34</t>
+          <t>L32</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -774,12 +774,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>t3_5</t>
+          <t>t3_3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prof. Vikram More</t>
+          <t>Prof. Amit Shah</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -792,12 +792,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>faculty35@example.edu</t>
+          <t>faculty33@example.edu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>F35</t>
+          <t>F33</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -820,12 +820,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>t3_6</t>
+          <t>t3_4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prof. Sanika Rane</t>
+          <t>Prof. Pooja Kulkarni</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -838,12 +838,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>faculty36@example.edu</t>
+          <t>faculty34@example.edu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>F36</t>
+          <t>F34</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -866,12 +866,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>t3_7</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prof. Omkar Kale</t>
+          <t>Prof. Sahil Desai</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -884,16 +884,16 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>faculty37@example.edu</t>
+          <t>lab34@example.edu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>F37</t>
+          <t>L34</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -912,12 +912,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>t5_0</t>
+          <t>t3_5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dr. Meera Nair</t>
+          <t>Prof. Vikram More</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -930,12 +930,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>faculty50@example.edu</t>
+          <t>faculty35@example.edu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>F50</t>
+          <t>F35</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -958,12 +958,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>t5_1</t>
+          <t>t3_6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prof. Sandeep Jadhav</t>
+          <t>Prof. Sanika Rane</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -976,12 +976,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>faculty51@example.edu</t>
+          <t>faculty36@example.edu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>F51</t>
+          <t>F36</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1004,12 +1004,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>t5_2</t>
+          <t>t3_7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prof. Neha Desai</t>
+          <t>Prof. Omkar Kale</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>faculty52@example.edu</t>
+          <t>faculty37@example.edu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>F52</t>
+          <t>F37</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1050,12 +1050,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>t5_3</t>
+          <t>t5_0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Prof. Kiran Rao</t>
+          <t>Dr. Meera Nair</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1068,12 +1068,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>faculty53@example.edu</t>
+          <t>faculty50@example.edu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>F53</t>
+          <t>F50</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1096,12 +1096,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>t5_4</t>
+          <t>t5_1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dr. Priya Menon</t>
+          <t>Prof. Sandeep Jadhav</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>faculty54@example.edu</t>
+          <t>faculty51@example.edu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>F54</t>
+          <t>F51</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1142,12 +1142,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>t5_5</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prof. Aditya Gokhale</t>
+          <t>Prof. Kunal Patil</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1160,16 +1160,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>faculty55@example.edu</t>
+          <t>lab51@example.edu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>F55</t>
+          <t>L51</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1188,12 +1188,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>t5_6</t>
+          <t>t5_2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dr. Snehal Shinde</t>
+          <t>Prof. Neha Desai</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>faculty56@example.edu</t>
+          <t>faculty52@example.edu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>F56</t>
+          <t>F52</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1234,12 +1234,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>t5_7</t>
+          <t>lt5_2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prof. Akash Pawar</t>
+          <t>Prof. Neelam Shah</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1252,16 +1252,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>faculty57@example.edu</t>
+          <t>lab52@example.edu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>F57</t>
+          <t>L52</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1280,12 +1280,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>t7_0</t>
+          <t>t5_3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dr. Shreya Kulkarni</t>
+          <t>Prof. Kiran Rao</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>faculty70@example.edu</t>
+          <t>faculty53@example.edu</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>F70</t>
+          <t>F53</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -1326,12 +1326,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>t7_1</t>
+          <t>t5_4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prof. Nikhil Sawant</t>
+          <t>Dr. Priya Menon</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>faculty71@example.edu</t>
+          <t>faculty54@example.edu</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>F71</t>
+          <t>F54</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -1372,12 +1372,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>t7_2</t>
+          <t>lt5_4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prof. Kavita Iyer</t>
+          <t>Prof. Varun Nair</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1390,16 +1390,16 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>faculty72@example.edu</t>
+          <t>lab54@example.edu</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>F72</t>
+          <t>L54</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1418,12 +1418,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>t7_3</t>
+          <t>t5_5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Prof. Rohit Bhosale</t>
+          <t>Prof. Aditya Gokhale</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>faculty73@example.edu</t>
+          <t>faculty55@example.edu</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>F73</t>
+          <t>F55</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -1464,12 +1464,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>t7_4</t>
+          <t>t5_6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dr. Aditi Naik</t>
+          <t>Dr. Snehal Shinde</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>faculty74@example.edu</t>
+          <t>faculty56@example.edu</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>F74</t>
+          <t>F56</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -1510,12 +1510,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>t7_5</t>
+          <t>t5_7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Prof. Sameer Pawar</t>
+          <t>Prof. Akash Pawar</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>faculty75@example.edu</t>
+          <t>faculty57@example.edu</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>F75</t>
+          <t>F57</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1556,12 +1556,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>t7_6</t>
+          <t>t7_0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Prof. Rutuja More</t>
+          <t>Dr. Shreya Kulkarni</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>faculty76@example.edu</t>
+          <t>faculty70@example.edu</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>F76</t>
+          <t>F70</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -1602,12 +1602,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>t7_7</t>
+          <t>t7_1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dr. Harsh Mehta</t>
+          <t>Prof. Nikhil Sawant</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>faculty77@example.edu</t>
+          <t>faculty71@example.edu</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>F77</t>
+          <t>F71</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -1640,6 +1640,420 @@
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>lt7_1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Prof. Tanvi Rao</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>20</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>lab71@example.edu</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>L71</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>6</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>t7_2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Prof. Kavita Iyer</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>faculty72@example.edu</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>F72</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>5</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>lt7_2</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Prof. Pranav More</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>20</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>lab72@example.edu</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>L72</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>t7_3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Prof. Rohit Bhosale</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>20</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>faculty73@example.edu</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>F73</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>t7_4</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Dr. Aditi Naik</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>faculty74@example.edu</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>F74</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>lt7_4</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Prof. Rohini Jadhav</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>20</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>lab74@example.edu</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>L74</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>6</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>t7_5</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Prof. Sameer Pawar</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>20</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>faculty75@example.edu</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>F75</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>t7_6</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Prof. Rutuja More</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>faculty76@example.edu</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>F76</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>5</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>t7_7</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Dr. Harsh Mehta</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>20</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>faculty77@example.edu</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>F77</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>17:45</t>
         </is>
@@ -2622,7 +3036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2892,7 +3306,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -2922,7 +3336,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2930,6 +3344,126 @@
         </is>
       </c>
       <c r="F10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IT Shared Lab 3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IT Shared Lab 4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IT Shared Lab 5</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IT Shared Lab 6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>20</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -3207,7 +3741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3236,6 +3770,546 @@
         <is>
           <t>strength</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>it3A1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>it3A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>it3A2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>it3A</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>it3A3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>it3A</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>it3B1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>it3B</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>it3B2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>it3B</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>it3B3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>it3B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>it3C1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>it3C</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>it3C2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>it3C</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>it3C3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>it3C</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>it5A1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>it5A2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>it5A3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>it5B1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>it5B2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>it5B3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>it5C1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>it5C2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>it5C3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>it7A1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>it7A2</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>it7A3</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>it7B1</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>it7B2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>it7B3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>it7C1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>it7C2</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>it7C3</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3372,7 +4446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3551,7 +4625,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -3560,12 +4634,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT302_B</t>
+          <t>IT302_A_b1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3575,28 +4649,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>t3_1</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>it3A1</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT302_C</t>
+          <t>IT302_A_b2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3606,23 +4690,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>t3_1</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
       <c r="H7" t="n">
         <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>it3A2</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT303_A</t>
+          <t>IT302_A_b3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3632,28 +4726,38 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT302</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>t3_2</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>it3A3</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IT303_B</t>
+          <t>IT302_B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3663,19 +4767,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT302</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>t3_2</t>
+          <t>t3_1</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -3684,69 +4788,89 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT303_C</t>
+          <t>IT302_B_b1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT302</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>t3_2</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>it3B1</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT304_A</t>
+          <t>IT302_B_b2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IT304</t>
+          <t>IT302</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>t3_3</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
       </c>
       <c r="H11" t="n">
         <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>it3B2</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT304_B</t>
+          <t>IT302_B_b3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3756,28 +4880,38 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IT304</t>
+          <t>IT302</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>t3_3</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
       </c>
       <c r="H12" t="n">
         <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>it3B3</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT304_C</t>
+          <t>IT302_C</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3787,12 +4921,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IT304</t>
+          <t>IT302</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>t3_3</t>
+          <t>t3_1</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -3808,69 +4942,89 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT305_A</t>
+          <t>IT302_C_b1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT302</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>t3_4</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
       <c r="H14" t="n">
         <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>it3C1</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT305_B</t>
+          <t>IT302_C_b2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT302</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>t3_4</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
       <c r="H15" t="n">
         <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>it3C2</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT305_C</t>
+          <t>IT302_C_b3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3880,28 +5034,38 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT302</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>t3_4</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
       <c r="H16" t="n">
         <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>it3C3</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT306_A</t>
+          <t>IT303_A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3911,16 +5075,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IT306</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>t3_5</t>
+          <t>t3_2</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -3932,69 +5096,89 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT306_B</t>
+          <t>IT303_A_b1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IT306</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>t3_5</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
       </c>
       <c r="H18" t="n">
         <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>it3A1</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IT306_C</t>
+          <t>IT303_A_b2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IT306</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>t3_5</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
       </c>
       <c r="H19" t="n">
         <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>it3A2</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ITE301_A</t>
+          <t>IT303_A_b3</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4004,28 +5188,38 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ITE301</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>t3_6</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
       </c>
       <c r="H20" t="n">
         <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>it3A3</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ITE301_B</t>
+          <t>IT303_B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4035,16 +5229,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ITE301</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>t3_6</t>
+          <t>t3_2</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -4056,69 +5250,89 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ITE301_C</t>
+          <t>IT303_B_b1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ITE301</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>t3_6</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
       </c>
       <c r="H22" t="n">
         <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>it3B1</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ITE302_A</t>
+          <t>IT303_B_b2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ITE302</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>t3_7</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
       </c>
       <c r="H23" t="n">
         <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>it3B2</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ITE302_B</t>
+          <t>IT303_B_b3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4128,28 +5342,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ITE302</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>t3_7</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
       </c>
       <c r="H24" t="n">
         <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>it3B3</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ITE302_C</t>
+          <t>IT303_C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -4159,16 +5383,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ITE302</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>t3_7</t>
+          <t>t3_2</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -4180,122 +5404,152 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT501_A</t>
+          <t>IT303_C_b1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IT501</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>t5_0</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
       </c>
       <c r="H26" t="n">
         <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>it3C1</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT501_B</t>
+          <t>IT303_C_b2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IT501</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>t5_0</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
       </c>
       <c r="H27" t="n">
         <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>it3C2</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT501_C</t>
+          <t>IT303_C_b3</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IT501</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>t5_0</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
       </c>
       <c r="H28" t="n">
         <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>it3C3</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT502_A</t>
+          <t>IT304_A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT304</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>t5_1</t>
+          <t>t3_3</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>4</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -4304,29 +5558,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT502_B</t>
+          <t>IT304_B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT304</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>t5_1</t>
+          <t>t3_3</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -4335,29 +5589,29 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT502_C</t>
+          <t>IT304_C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT304</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>t5_1</t>
+          <t>t3_3</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>4</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -4366,29 +5620,29 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT503_A</t>
+          <t>IT305_A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>t5_2</t>
+          <t>t3_4</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4397,119 +5651,149 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT503_B</t>
+          <t>IT305_A_b1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>t5_2</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>1</v>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
       <c r="H33" t="n">
         <v>0</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>it3A1</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IT503_C</t>
+          <t>IT305_A_b2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>t5_2</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>1</v>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>it3A2</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT504_A</t>
+          <t>IT305_A_b3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IT504</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>t5_3</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
       </c>
       <c r="H35" t="n">
         <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>it3A3</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IT504_B</t>
+          <t>IT305_B</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IT504</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>t5_3</t>
+          <t>t3_4</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -4521,122 +5805,152 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT504_C</t>
+          <t>IT305_B_b1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IT504</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>t5_3</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
       </c>
       <c r="H37" t="n">
         <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>it3B1</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT505_A</t>
+          <t>IT305_B_b2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>t5_4</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>1</v>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>0</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>it3B2</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IT505_B</t>
+          <t>IT305_B_b3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>t5_4</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>1</v>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>0</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>it3B3</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IT505_C</t>
+          <t>IT305_C</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>t5_4</t>
+          <t>t3_4</t>
         </is>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -4645,119 +5959,149 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT506_A</t>
+          <t>IT305_C_b1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IT506</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>t5_5</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
       </c>
       <c r="H41" t="n">
         <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>it3C1</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IT506_B</t>
+          <t>IT305_C_b2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IT506</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>t5_5</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
       </c>
       <c r="H42" t="n">
         <v>0</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>it3C2</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT506_C</t>
+          <t>IT305_C_b3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IT506</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>t5_5</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
       </c>
       <c r="H43" t="n">
         <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>it3C3</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ITE501_A</t>
+          <t>IT306_A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ITE501</t>
+          <t>IT306</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>t5_6</t>
+          <t>t3_5</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -4769,26 +6113,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ITE501_B</t>
+          <t>IT306_B</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ITE501</t>
+          <t>IT306</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>t5_6</t>
+          <t>t3_5</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4800,26 +6144,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ITE501_C</t>
+          <t>IT306_C</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ITE501</t>
+          <t>IT306</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>t5_6</t>
+          <t>t3_5</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -4831,22 +6175,22 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ITE502_A</t>
+          <t>ITE301_A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ITE502</t>
+          <t>ITE301</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>t5_7</t>
+          <t>t3_6</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -4862,22 +6206,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ITE502_B</t>
+          <t>ITE301_B</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ITE502</t>
+          <t>ITE301</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>t5_7</t>
+          <t>t3_6</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -4893,22 +6237,22 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ITE502_C</t>
+          <t>ITE301_C</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ITE502</t>
+          <t>ITE301</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>t5_7</t>
+          <t>t3_6</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -4924,26 +6268,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT701_A</t>
+          <t>ITE302_A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>it7A</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IT701</t>
+          <t>ITE302</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>t7_0</t>
+          <t>t3_7</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -4955,26 +6299,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IT701_B</t>
+          <t>ITE302_B</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>it7B</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IT701</t>
+          <t>ITE302</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>t7_0</t>
+          <t>t3_7</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -4986,26 +6330,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IT701_C</t>
+          <t>ITE302_C</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>it7C</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IT701</t>
+          <t>ITE302</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>t7_0</t>
+          <t>t3_7</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
@@ -5017,29 +6361,29 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IT702_A</t>
+          <t>IT501_A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>it7A</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IT702</t>
+          <t>IT501</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>t7_1</t>
+          <t>t5_0</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>4</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -5048,29 +6392,29 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT702_B</t>
+          <t>IT501_B</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>it7B</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IT702</t>
+          <t>IT501</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>t7_1</t>
+          <t>t5_0</t>
         </is>
       </c>
       <c r="E54" t="n">
         <v>4</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -5079,29 +6423,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IT702_C</t>
+          <t>IT501_C</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>it7C</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IT702</t>
+          <t>IT501</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>t7_1</t>
+          <t>t5_0</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -5110,29 +6454,29 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT703_A</t>
+          <t>IT502_A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>it7A</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IT703</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>t7_2</t>
+          <t>t5_1</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>4</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -5141,115 +6485,145 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT703_B</t>
+          <t>IT502_A_b1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>it7B</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IT703</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>t7_2</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>it5A1</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT703_C</t>
+          <t>IT502_A_b2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>it7C</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IT703</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>t7_2</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
+      </c>
       <c r="H58" t="n">
         <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>it5A2</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT704_A</t>
+          <t>IT502_A_b3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>it7A</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IT704</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>t7_3</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
       </c>
       <c r="H59" t="n">
         <v>0</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>it5A3</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT704_B</t>
+          <t>IT502_B</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>it7B</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IT704</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>t7_3</t>
+          <t>t5_1</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -5265,122 +6639,152 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IT704_C</t>
+          <t>IT502_B_b1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>it7C</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IT704</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>t7_3</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
       </c>
       <c r="H61" t="n">
         <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>it5B1</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IT705_A</t>
+          <t>IT502_B_b2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>it7A</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IT705</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>t7_4</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
       <c r="H62" t="n">
         <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>it5B2</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IT705_B</t>
+          <t>IT502_B_b3</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>it7B</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IT705</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>t7_4</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
       <c r="H63" t="n">
         <v>0</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>it5B3</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IT705_C</t>
+          <t>IT502_C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>it7C</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IT705</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>t7_4</t>
+          <t>t5_1</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -5389,119 +6793,149 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IT706_A</t>
+          <t>IT502_C_b1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>it7A</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IT706</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>t7_5</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
       </c>
       <c r="H65" t="n">
         <v>0</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>it5C1</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IT706_B</t>
+          <t>IT502_C_b2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>it7B</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IT706</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>t7_5</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
       </c>
       <c r="H66" t="n">
         <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>it5C2</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IT706_C</t>
+          <t>IT502_C_b3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>it7C</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IT706</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>t7_5</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
       </c>
       <c r="H67" t="n">
         <v>0</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>it5C3</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ITE701_A</t>
+          <t>IT503_A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>it7A</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ITE701</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>t7_6</t>
+          <t>t5_2</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -5513,119 +6947,149 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ITE701_B</t>
+          <t>IT503_A_b1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>it7B</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ITE701</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>t7_6</t>
+          <t>lt5_2</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
       </c>
       <c r="H69" t="n">
         <v>0</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>it5A1</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ITE701_C</t>
+          <t>IT503_A_b2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>it7C</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ITE701</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>t7_6</t>
+          <t>lt5_2</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
       </c>
       <c r="H70" t="n">
         <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>it5A2</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ITE702_A</t>
+          <t>IT503_A_b3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>it7A</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ITE702</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>t7_7</t>
+          <t>lt5_2</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
       </c>
       <c r="H71" t="n">
         <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>it5A3</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ITE702_B</t>
+          <t>IT503_B</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>it7B</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ITE702</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>t7_7</t>
+          <t>t5_2</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -5637,31 +7101,2962 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>IT503_B_b1</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IT503</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>lt5_2</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>it5B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>IT503_B_b2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>IT503</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>lt5_2</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>it5B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>IT503_B_b3</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>IT503</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>lt5_2</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>it5B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IT503_C</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>IT503</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>t5_2</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>IT503_C_b1</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>IT503</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>lt5_2</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>it5C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>IT503_C_b2</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>IT503</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>lt5_2</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>it5C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>IT503_C_b3</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>IT503</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>lt5_2</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>it5C3</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>IT504_A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>IT504</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>t5_3</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>IT504_B</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>IT504</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>t5_3</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>IT504_C</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>IT504</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>t5_3</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>IT505_A</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>t5_4</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>3</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>IT505_A_b1</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>lt5_4</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>it5A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>IT505_A_b2</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>lt5_4</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>it5A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>IT505_A_b3</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>lt5_4</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>it5A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>IT505_B</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>t5_4</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>3</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>IT505_B_b1</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>lt5_4</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>it5B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>IT505_B_b2</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>lt5_4</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>it5B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>IT505_B_b3</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>lt5_4</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>it5B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>IT505_C</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>t5_4</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>IT505_C_b1</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>lt5_4</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>it5C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>IT505_C_b2</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>lt5_4</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>it5C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>IT505_C_b3</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>IT505</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>lt5_4</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>it5C3</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>IT506_A</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>IT506</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>t5_5</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>IT506_B</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>IT506</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>t5_5</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>IT506_C</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>IT506</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>t5_5</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ITE501_A</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ITE501</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>t5_6</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ITE501_B</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ITE501</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>t5_6</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ITE501_C</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ITE501</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>t5_6</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ITE502_A</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>it5A</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ITE502</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>t5_7</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ITE502_B</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>it5B</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ITE502</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>t5_7</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ITE502_C</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>it5C</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ITE502</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>t5_7</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>IT701_A</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>IT701</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>t7_0</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>4</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>IT701_B</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>IT701</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>t7_0</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>4</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>IT701_C</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>IT701</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>t7_0</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>IT702_A</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>t7_1</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>IT702_A_b1</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>lt7_1</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>it7A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>IT702_A_b2</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>lt7_1</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>it7A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>IT702_A_b3</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>lt7_1</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>it7A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>IT702_B</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>t7_1</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>4</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>IT702_B_b1</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>lt7_1</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>it7B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>IT702_B_b2</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>lt7_1</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>it7B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>IT702_B_b3</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>lt7_1</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>it7B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>IT702_C</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>t7_1</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>IT702_C_b1</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>lt7_1</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>it7C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>IT702_C_b2</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>lt7_1</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>it7C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>IT702_C_b3</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>IT702</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>lt7_1</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>it7C3</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>IT703_A</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>t7_2</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>4</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>IT703_A_b1</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>lt7_2</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>it7A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>IT703_A_b2</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>lt7_2</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>it7A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>IT703_A_b3</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>lt7_2</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>it7A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>IT703_B</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>t7_2</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>4</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>IT703_B_b1</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>lt7_2</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>it7B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>IT703_B_b2</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>lt7_2</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>it7B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>IT703_B_b3</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>lt7_2</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>it7B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>IT703_C</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>t7_2</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>4</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>IT703_C_b1</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>lt7_2</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>it7C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>IT703_C_b2</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>lt7_2</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>it7C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>IT703_C_b3</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>IT703</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>lt7_2</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>it7C3</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>IT704_A</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>IT704</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>t7_3</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>4</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>IT704_B</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>IT704</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>t7_3</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>4</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>IT704_C</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>IT704</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>t7_3</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>4</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>IT705_A</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>t7_4</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>3</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>IT705_A_b1</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>lt7_4</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>it7A1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>IT705_A_b2</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>lt7_4</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>it7A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>IT705_A_b3</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>lt7_4</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>it7A3</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>IT705_B</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>t7_4</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>3</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>IT705_B_b1</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>lt7_4</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>it7B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>IT705_B_b2</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>lt7_4</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>it7B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>IT705_B_b3</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>lt7_4</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>it7B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>IT705_C</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>t7_4</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>3</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>IT705_C_b1</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>lt7_4</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>it7C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>IT705_C_b2</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>lt7_4</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>it7C2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>IT705_C_b3</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>IT705</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>lt7_4</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>it7C3</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>IT706_A</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>IT706</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>t7_5</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>3</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>IT706_B</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>IT706</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>t7_5</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>3</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>IT706_C</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>IT706</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>t7_5</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>3</v>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ITE701_A</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>ITE701</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>t7_6</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>2</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ITE701_B</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ITE701</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>t7_6</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>2</v>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ITE701_C</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>it7C</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>ITE701</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>t7_6</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>2</v>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ITE702_A</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>it7A</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ITE702</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>t7_7</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>ITE702_B</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>it7B</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>ITE702</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>t7_7</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>ITE702_C</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B154" t="inlineStr">
         <is>
           <t>it7C</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C154" t="inlineStr">
         <is>
           <t>ITE702</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D154" t="inlineStr">
         <is>
           <t>t7_7</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E154" t="n">
         <v>2</v>
       </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="n">
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5676,7 +10071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5766,34 +10161,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lecture_slots</t>
+          <t>spread_lectures</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lab_slots</t>
+          <t>lecture_slots</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>lab_slots</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>project_slots</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>4</t>
         </is>

--- a/sample_data/it_presentation.xlsx
+++ b/sample_data/it_presentation.xlsx
@@ -2070,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2432,21 +2432,21 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT501</t>
+          <t>IT3P</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operating Systems</t>
+          <t>Mini Project</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IT501</t>
+          <t>IT3P</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>project</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -2468,17 +2468,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT501</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Computer Networks</t>
+          <t>Operating Systems</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT501</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -2494,27 +2494,27 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Software Engineering</t>
+          <t>Computer Networks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -2540,17 +2540,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT504</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Automata &amp; Compiler Design</t>
+          <t>Software Engineering</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IT504</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -2566,27 +2566,27 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT504</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Advanced Database Systems</t>
+          <t>Automata &amp; Compiler Design</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT504</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -2602,27 +2602,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT506</t>
+          <t>IT505</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Information Security</t>
+          <t>Advanced Database Systems</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IT506</t>
+          <t>IT505</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -2638,68 +2638,63 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ITE501</t>
+          <t>IT506</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Information Security</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ITE501</t>
+          <t>IT506</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>it</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>es5</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>theory</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ITE502</t>
+          <t>ITE501</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cloud Fundamentals</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ITE502</t>
+          <t>ITE501</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -2730,57 +2725,62 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT701</t>
+          <t>ITE502</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Cloud Fundamentals</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IT701</t>
+          <t>ITE502</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>it</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>es5</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>theory</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IT702</t>
+          <t>IT5P</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Big Data Analytics</t>
+          <t>Mini Project</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IT702</t>
+          <t>IT5P</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -2792,27 +2792,27 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>project</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IT703</t>
+          <t>IT701</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IT703</t>
+          <t>IT701</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2828,27 +2828,27 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>theory</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT704</t>
+          <t>IT702</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Distributed Systems</t>
+          <t>Big Data Analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IT704</t>
+          <t>IT702</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2864,27 +2864,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT705</t>
+          <t>IT703</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cyber Security</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IT705</t>
+          <t>IT703</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2904,23 +2904,23 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT706</t>
+          <t>IT704</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DevOps &amp; Software Architecture</t>
+          <t>Distributed Systems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IT706</t>
+          <t>IT704</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2940,89 +2940,197 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ITE701</t>
+          <t>IT705</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Internet of Things</t>
+          <t>Cyber Security</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ITE701</t>
+          <t>IT705</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>7</v>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>it</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>es7</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>theory</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ITE702</t>
+          <t>IT706</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Blockchain Technology</t>
+          <t>DevOps &amp; Software Architecture</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ITE702</t>
+          <t>IT706</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>7</v>
       </c>
       <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>theory</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ITE701</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Internet of Things</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ITE701</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="b">
         <v>1</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>es7</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>theory</t>
         </is>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ITE702</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Blockchain Technology</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ITE702</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>es7</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>theory</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IT7P</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mini Project</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>IT7P</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3366,7 +3474,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -3456,7 +3564,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4446,7 +4554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I154"/>
+  <dimension ref="A1:J109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4458,6 +4566,7 @@
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4506,6 +4615,11 @@
           <t>batch_id</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>project_hours</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4675,12 +4789,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IT302_A_b2</t>
+          <t>IT302_B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4690,38 +4804,28 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>lt3_1</t>
+          <t>t3_1</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>it3A2</t>
-        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT302_A_b3</t>
+          <t>IT302_B_b1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4742,7 +4846,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>lab6</t>
+          <t>lab1</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -4750,19 +4854,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>it3A3</t>
+          <t>it3B1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IT302_B</t>
+          <t>IT302_C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4788,12 +4892,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IT302_B_b1</t>
+          <t>IT302_C_b1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4814,7 +4918,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>lab1</t>
+          <t>lab4</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -4822,70 +4926,60 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>it3B1</t>
+          <t>it3C1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT302_B_b2</t>
+          <t>IT303_A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IT302</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>lt3_1</t>
+          <t>t3_2</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>lab2</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>it3B2</t>
-        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IT302_B_b3</t>
+          <t>IT303_A_b2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IT302</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>lt3_1</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4896,7 +4990,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>lab3</t>
+          <t>lab5</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -4904,29 +4998,29 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>it3B3</t>
+          <t>it3A2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT302_C</t>
+          <t>IT303_B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IT302</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>t3_1</t>
+          <t>t3_2</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4942,22 +5036,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IT302_C_b1</t>
+          <t>IT303_B_b2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IT302</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>lt3_1</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -4968,7 +5062,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>lab4</t>
+          <t>lab2</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -4976,14 +5070,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>it3C1</t>
+          <t>it3B2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT302_C_b2</t>
+          <t>IT303_C</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4993,38 +5087,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IT302</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>lt3_1</t>
+          <t>t3_2</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>it3C2</t>
-        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT302_C_b3</t>
+          <t>IT303_C_b2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5034,12 +5118,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IT302</t>
+          <t>IT303</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>lt3_1</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -5050,7 +5134,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>lab6</t>
+          <t>lab5</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -5058,14 +5142,14 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>it3C3</t>
+          <t>it3C2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT303_A</t>
+          <t>IT304_A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5075,12 +5159,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT304</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>t3_2</t>
+          <t>t3_3</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -5096,89 +5180,69 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IT303_A_b1</t>
+          <t>IT304_B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT304</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>lt3_2</t>
+          <t>t3_3</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>it3A1</t>
-        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IT303_A_b2</t>
+          <t>IT304_C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT304</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>lt3_2</t>
+          <t>t3_3</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>it3A2</t>
-        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IT303_A_b3</t>
+          <t>IT305_A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5188,69 +5252,69 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>lt3_2</t>
+          <t>t3_4</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>it3A3</t>
-        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT303_B</t>
+          <t>IT305_A_b3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>t3_2</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
       </c>
       <c r="H21" t="n">
         <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>it3A3</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT303_B_b1</t>
+          <t>IT305_B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5260,38 +5324,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>lt3_2</t>
+          <t>t3_4</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>lab1</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>it3B1</t>
-        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT303_B_b2</t>
+          <t>IT305_B_b3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5301,12 +5355,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>lt3_2</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -5317,7 +5371,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>lab2</t>
+          <t>lab3</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -5325,55 +5379,45 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>it3B2</t>
+          <t>it3B3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IT303_B_b3</t>
+          <t>IT305_C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>lt3_2</t>
+          <t>t3_4</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>lab3</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>it3B3</t>
-        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IT303_C</t>
+          <t>IT305_C_b3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5383,110 +5427,100 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT305</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>t3_2</t>
+          <t>lt3_4</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
       </c>
       <c r="H25" t="n">
         <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>it3C3</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT303_C_b1</t>
+          <t>IT306_A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it3A</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT306</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>lt3_2</t>
+          <t>t3_5</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>it3C1</t>
-        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT303_C_b2</t>
+          <t>IT306_B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT306</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>lt3_2</t>
+          <t>t3_5</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>it3C2</t>
-        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT303_C_b3</t>
+          <t>IT306_C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5496,38 +5530,28 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IT303</t>
+          <t>IT306</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>lt3_2</t>
+          <t>t3_5</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>it3C3</t>
-        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT304_A</t>
+          <t>ITE301_A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5537,16 +5561,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IT304</t>
+          <t>ITE301</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>t3_3</t>
+          <t>t3_6</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -5558,7 +5582,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT304_B</t>
+          <t>ITE301_B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5568,16 +5592,16 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>IT304</t>
+          <t>ITE301</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>t3_3</t>
+          <t>t3_6</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -5589,7 +5613,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IT304_C</t>
+          <t>ITE301_C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5599,16 +5623,16 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IT304</t>
+          <t>ITE301</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>t3_3</t>
+          <t>t3_6</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -5620,7 +5644,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IT305_A</t>
+          <t>ITE302_A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5630,16 +5654,16 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>ITE302</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>t3_4</t>
+          <t>t3_7</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -5651,89 +5675,69 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IT305_A_b1</t>
+          <t>ITE302_B</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it3B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>ITE302</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>lt3_4</t>
+          <t>t3_7</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>it3A1</t>
-        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IT305_A_b2</t>
+          <t>ITE302_C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>ITE302</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>lt3_4</t>
+          <t>t3_7</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>it3A2</t>
-        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT305_A_b3</t>
+          <t>IT3P_A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5743,38 +5747,31 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT3P</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>lt3_4</t>
+          <t>lt3_1</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
         <v>1</v>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>it3A3</t>
-        </is>
+      <c r="J35" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IT305_B</t>
+          <t>IT3P_B</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5784,38 +5781,41 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT3P</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>t3_4</t>
+          <t>lt3_2</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT305_B_b1</t>
+          <t>IT3P_C</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it3C</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT3P</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5827,127 +5827,100 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>1</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>lab1</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>it3B1</t>
-        </is>
+      <c r="J37" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT305_B_b2</t>
+          <t>IT501_A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT501</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>lt3_4</t>
+          <t>t5_0</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>lab2</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>it3B2</t>
-        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IT305_B_b3</t>
+          <t>IT501_B</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT501</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>lt3_4</t>
+          <t>t5_0</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>lab3</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>it3B3</t>
-        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IT305_C</t>
+          <t>IT501_C</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT501</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>t3_4</t>
+          <t>t5_0</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -5959,63 +5932,53 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT305_C_b1</t>
+          <t>IT502_A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>lt3_4</t>
+          <t>t5_1</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>it3C1</t>
-        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IT305_C_b2</t>
+          <t>IT502_A_b1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>lt3_4</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -6026,7 +5989,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>lab5</t>
+          <t>lab1</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -6034,105 +5997,105 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>it3C2</t>
+          <t>it5A1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>IT305_C_b3</t>
+          <t>IT502_B</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IT305</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>lt3_4</t>
+          <t>t5_1</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>it3C3</t>
-        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT306_A</t>
+          <t>IT502_B_b1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IT306</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>t3_5</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
       </c>
       <c r="H44" t="n">
         <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>it5B1</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IT306_B</t>
+          <t>IT502_C</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IT306</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>t3_5</t>
+          <t>t5_1</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -6144,57 +6107,67 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT306_C</t>
+          <t>IT502_C_b1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IT306</t>
+          <t>IT502</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>t3_5</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
       </c>
       <c r="H46" t="n">
         <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>it5C1</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ITE301_A</t>
+          <t>IT503_A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ITE301</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>t3_6</t>
+          <t>t5_2</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -6206,57 +6179,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ITE301_B</t>
+          <t>IT503_A_b2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ITE301</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>t3_6</t>
+          <t>lt5_2</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
       </c>
       <c r="H48" t="n">
         <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>it5A2</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ITE301_C</t>
+          <t>IT503_B</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ITE301</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>t3_6</t>
+          <t>t5_2</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -6268,57 +6251,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ITE302_A</t>
+          <t>IT503_B_b2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>it3A</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ITE302</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>t3_7</t>
+          <t>lt5_2</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>lab5</t>
+        </is>
       </c>
       <c r="H50" t="n">
         <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>it5B2</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ITE302_B</t>
+          <t>IT503_C</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>it3B</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ITE302</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>t3_7</t>
+          <t>t5_2</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -6330,38 +6323,48 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ITE302_C</t>
+          <t>IT503_C_b2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>it3C</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ITE302</t>
+          <t>IT503</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>t3_7</t>
+          <t>lt5_2</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>lab2</t>
+        </is>
       </c>
       <c r="H52" t="n">
         <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>it5C2</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>IT501_A</t>
+          <t>IT504_A</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6371,12 +6374,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>IT501</t>
+          <t>IT504</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>t5_0</t>
+          <t>t5_3</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6392,7 +6395,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT501_B</t>
+          <t>IT504_B</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6402,12 +6405,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IT501</t>
+          <t>IT504</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>t5_0</t>
+          <t>t5_3</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -6423,7 +6426,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IT501_C</t>
+          <t>IT504_C</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6433,12 +6436,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IT501</t>
+          <t>IT504</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>t5_0</t>
+          <t>t5_3</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6454,7 +6457,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT502_A</t>
+          <t>IT505_A</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6464,16 +6467,16 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT505</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>t5_1</t>
+          <t>t5_4</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -6485,7 +6488,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT502_A_b1</t>
+          <t>IT505_A_b3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6495,12 +6498,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT505</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>lt5_1</t>
+          <t>lt5_4</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6511,7 +6514,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>lab1</t>
+          <t>lab3</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -6519,70 +6522,60 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>it5A1</t>
+          <t>it5A3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT502_A_b2</t>
+          <t>IT505_B</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT505</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>lt5_1</t>
+          <t>t5_4</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>lab2</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>it5A2</t>
-        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT502_A_b3</t>
+          <t>IT505_B_b3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT505</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>lt5_1</t>
+          <t>lt5_4</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6593,7 +6586,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>lab3</t>
+          <t>lab6</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -6601,33 +6594,33 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>it5A3</t>
+          <t>it5B3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT502_B</t>
+          <t>IT505_C</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT505</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>t5_1</t>
+          <t>t5_4</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -6639,22 +6632,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>IT502_B_b1</t>
+          <t>IT505_C_b3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT505</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>lt5_1</t>
+          <t>lt5_4</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6665,7 +6658,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>lab4</t>
+          <t>lab3</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -6673,55 +6666,45 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>it5B1</t>
+          <t>it5C3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IT502_B_b2</t>
+          <t>IT506_A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT506</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>lt5_1</t>
+          <t>t5_5</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F62" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>it5B2</t>
-        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IT502_B_b3</t>
+          <t>IT506_B</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6731,38 +6714,28 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT506</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>lt5_1</t>
+          <t>t5_5</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>it5B3</t>
-        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IT502_C</t>
+          <t>IT506_C</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6772,16 +6745,16 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>IT506</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>t5_1</t>
+          <t>t5_5</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -6793,89 +6766,69 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IT502_C_b1</t>
+          <t>ITE501_A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it5A</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>ITE501</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>lt5_1</t>
+          <t>t5_6</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>lab1</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>it5C1</t>
-        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IT502_C_b2</t>
+          <t>ITE501_B</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>ITE501</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>lt5_1</t>
+          <t>t5_6</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>lab2</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>it5C2</t>
-        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IT502_C_b3</t>
+          <t>ITE501_C</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6885,38 +6838,28 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>IT502</t>
+          <t>ITE501</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>lt5_1</t>
+          <t>t5_6</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>lab3</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>it5C3</t>
-        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IT503_A</t>
+          <t>ITE502_A</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6926,16 +6869,16 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>ITE502</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>t5_2</t>
+          <t>t5_7</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -6947,89 +6890,69 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IT503_A_b1</t>
+          <t>ITE502_B</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it5B</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>ITE502</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>lt5_2</t>
+          <t>t5_7</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>lab1</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>it5A1</t>
-        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT503_A_b2</t>
+          <t>ITE502_C</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>ITE502</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>lt5_2</t>
+          <t>t5_7</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>lab2</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>it5A2</t>
-        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT503_A_b3</t>
+          <t>IT5P_A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7039,38 +6962,31 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT5P</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>lt5_2</t>
+          <t>lt5_1</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
         <v>1</v>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>lab3</t>
-        </is>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>it5A3</t>
-        </is>
+      <c r="J71" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IT503_B</t>
+          <t>IT5P_B</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7080,166 +6996,142 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT5P</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>t5_2</t>
+          <t>lt5_2</t>
         </is>
       </c>
       <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
         <v>4</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT503_B_b1</t>
+          <t>IT5P_C</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it5C</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT5P</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>lt5_2</t>
+          <t>lt5_4</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
         <v>1</v>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>it5B1</t>
-        </is>
+      <c r="J73" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IT503_B_b2</t>
+          <t>IT701_A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it7A</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT701</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>lt5_2</t>
+          <t>t7_0</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>it5B2</t>
-        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IT503_B_b3</t>
+          <t>IT701_B</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT701</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>lt5_2</t>
+          <t>t7_0</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>it5B3</t>
-        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IT503_C</t>
+          <t>IT701_C</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT701</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>t5_2</t>
+          <t>t7_0</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -7255,63 +7147,53 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IT503_C_b1</t>
+          <t>IT702_A</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7A</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT702</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>lt5_2</t>
+          <t>t7_1</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F77" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>lab1</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>it5C1</t>
-        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IT503_C_b2</t>
+          <t>IT702_A_b1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7A</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT702</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>lt5_2</t>
+          <t>lt7_1</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -7322,7 +7204,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>lab2</t>
+          <t>lab4</t>
         </is>
       </c>
       <c r="H78" t="n">
@@ -7330,101 +7212,101 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>it5C2</t>
+          <t>it7A1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IT503_C_b3</t>
+          <t>IT702_B</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>IT503</t>
+          <t>IT702</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>lt5_2</t>
+          <t>t7_1</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>lab3</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>it5C3</t>
-        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IT504_A</t>
+          <t>IT702_B_b1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>IT504</t>
+          <t>IT702</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>t5_3</t>
+          <t>lt7_1</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>lab1</t>
+        </is>
       </c>
       <c r="H80" t="n">
         <v>0</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>it7B1</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IT504_B</t>
+          <t>IT702_C</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IT504</t>
+          <t>IT702</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>t5_3</t>
+          <t>t7_1</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -7440,57 +7322,67 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>IT504_C</t>
+          <t>IT702_C_b1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IT504</t>
+          <t>IT702</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>t5_3</t>
+          <t>lt7_1</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>lab4</t>
+        </is>
       </c>
       <c r="H82" t="n">
         <v>0</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>it7C1</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IT505_A</t>
+          <t>IT703_A</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it7A</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT703</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>t5_4</t>
+          <t>t7_2</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
@@ -7502,22 +7394,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IT505_A_b1</t>
+          <t>IT703_A_b2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it7A</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT703</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>lt5_4</t>
+          <t>lt7_2</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -7528,7 +7420,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>lab1</t>
+          <t>lab5</t>
         </is>
       </c>
       <c r="H84" t="n">
@@ -7536,70 +7428,60 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>it5A1</t>
+          <t>it7A2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IT505_A_b2</t>
+          <t>IT703_B</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT703</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>lt5_4</t>
+          <t>t7_2</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>lab2</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>it5A2</t>
-        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IT505_A_b3</t>
+          <t>IT703_B_b2</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT703</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>lt5_4</t>
+          <t>lt7_2</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -7610,7 +7492,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>lab3</t>
+          <t>lab2</t>
         </is>
       </c>
       <c r="H86" t="n">
@@ -7618,33 +7500,33 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>it5A3</t>
+          <t>it7B2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IT505_B</t>
+          <t>IT703_C</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT703</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>t5_4</t>
+          <t>t7_2</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -7656,22 +7538,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IT505_B_b1</t>
+          <t>IT703_C_b2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT703</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>lt5_4</t>
+          <t>lt7_2</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -7682,7 +7564,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>lab4</t>
+          <t>lab5</t>
         </is>
       </c>
       <c r="H88" t="n">
@@ -7690,115 +7572,95 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>it5B1</t>
+          <t>it7C2</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IT505_B_b2</t>
+          <t>IT704_A</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it7A</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT704</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>lt5_4</t>
+          <t>t7_3</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>it5B2</t>
-        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IT505_B_b3</t>
+          <t>IT704_B</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT704</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>lt5_4</t>
+          <t>t7_3</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>it5B3</t>
-        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IT505_C</t>
+          <t>IT704_C</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT704</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>t5_4</t>
+          <t>t7_3</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -7810,63 +7672,53 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IT505_C_b1</t>
+          <t>IT705_A</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7A</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT705</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>lt5_4</t>
+          <t>t7_4</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>lab1</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>it5C1</t>
-        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IT505_C_b2</t>
+          <t>IT705_A_b3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7A</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT705</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>lt5_4</t>
+          <t>lt7_4</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -7877,7 +7729,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>lab2</t>
+          <t>lab6</t>
         </is>
       </c>
       <c r="H93" t="n">
@@ -7885,101 +7737,101 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>it5C2</t>
+          <t>it7A3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IT505_C_b3</t>
+          <t>IT705_B</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IT505</t>
+          <t>IT705</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>lt5_4</t>
+          <t>t7_4</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F94" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>lab3</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>it5C3</t>
-        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IT506_A</t>
+          <t>IT705_B_b3</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>IT506</t>
+          <t>IT705</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>t5_5</t>
+          <t>lt7_4</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>lab3</t>
+        </is>
       </c>
       <c r="H95" t="n">
         <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>it7B3</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IT506_B</t>
+          <t>IT705_C</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IT506</t>
+          <t>IT705</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>t5_5</t>
+          <t>t7_4</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -7995,57 +7847,67 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IT506_C</t>
+          <t>IT705_C_b3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IT506</t>
+          <t>IT705</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>t5_5</t>
+          <t>lt7_4</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>lab6</t>
+        </is>
       </c>
       <c r="H97" t="n">
         <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>it7C3</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ITE501_A</t>
+          <t>IT706_A</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it7A</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ITE501</t>
+          <t>IT706</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>t5_6</t>
+          <t>t7_5</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
@@ -8057,26 +7919,26 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ITE501_B</t>
+          <t>IT706_B</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ITE501</t>
+          <t>IT706</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>t5_6</t>
+          <t>t7_5</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F99" t="n">
         <v>0</v>
@@ -8088,26 +7950,26 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ITE501_C</t>
+          <t>IT706_C</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ITE501</t>
+          <t>IT706</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>t5_6</t>
+          <t>t7_5</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F100" t="n">
         <v>0</v>
@@ -8119,22 +7981,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ITE502_A</t>
+          <t>ITE701_A</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>it5A</t>
+          <t>it7A</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ITE502</t>
+          <t>ITE701</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>t5_7</t>
+          <t>t7_6</t>
         </is>
       </c>
       <c r="E101" t="n">
@@ -8150,22 +8012,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ITE502_B</t>
+          <t>ITE701_B</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>it5B</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ITE502</t>
+          <t>ITE701</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>t5_7</t>
+          <t>t7_6</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -8181,22 +8043,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ITE502_C</t>
+          <t>ITE701_C</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>it5C</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ITE502</t>
+          <t>ITE701</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>t5_7</t>
+          <t>t7_6</t>
         </is>
       </c>
       <c r="E103" t="n">
@@ -8212,7 +8074,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>IT701_A</t>
+          <t>ITE702_A</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -8222,16 +8084,16 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IT701</t>
+          <t>ITE702</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>t7_0</t>
+          <t>t7_7</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -8243,7 +8105,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>IT701_B</t>
+          <t>ITE702_B</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -8253,16 +8115,16 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IT701</t>
+          <t>ITE702</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>t7_0</t>
+          <t>t7_7</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
@@ -8274,7 +8136,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>IT701_C</t>
+          <t>ITE702_C</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -8284,16 +8146,16 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IT701</t>
+          <t>ITE702</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>t7_0</t>
+          <t>t7_7</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -8305,7 +8167,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IT702_A</t>
+          <t>IT7P_A</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8315,1749 +8177,93 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IT702</t>
+          <t>IT7P</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>t7_1</t>
+          <t>lt7_1</t>
         </is>
       </c>
       <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
         <v>4</v>
-      </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IT702_A_b1</t>
+          <t>IT7P_B</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>it7A</t>
+          <t>it7B</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>IT702</t>
+          <t>IT7P</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>lt7_1</t>
+          <t>lt7_2</t>
         </is>
       </c>
       <c r="E108" t="n">
         <v>0</v>
       </c>
       <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
         <v>1</v>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>it7A1</t>
-        </is>
+      <c r="J108" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IT702_A_b2</t>
+          <t>IT7P_C</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>it7A</t>
+          <t>it7C</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>IT702</t>
+          <t>IT7P</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>lt7_1</t>
+          <t>lt7_4</t>
         </is>
       </c>
       <c r="E109" t="n">
         <v>0</v>
       </c>
       <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
         <v>1</v>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>it7A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>IT702_A_b3</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>IT702</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>lt7_1</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>it7A3</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>IT702_B</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>IT702</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>t7_1</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
+      <c r="J109" t="n">
         <v>4</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>IT702_B_b1</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>IT702</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>lt7_1</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>lab1</t>
-        </is>
-      </c>
-      <c r="H112" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>it7B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>IT702_B_b2</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>IT702</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>lt7_1</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>lab2</t>
-        </is>
-      </c>
-      <c r="H113" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>it7B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>IT702_B_b3</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>IT702</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>lt7_1</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="n">
-        <v>1</v>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>lab3</t>
-        </is>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>it7B3</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>IT702_C</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>IT702</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>t7_1</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>4</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>IT702_C_b1</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>IT702</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>lt7_1</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>it7C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>IT702_C_b2</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>IT702</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>lt7_1</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>0</v>
-      </c>
-      <c r="F117" t="n">
-        <v>1</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
-      </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>it7C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>IT702_C_b3</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>IT702</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>lt7_1</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>it7C3</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>IT703_A</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>t7_2</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>4</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>IT703_A_b1</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>lt7_2</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>it7A1</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>IT703_A_b2</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>lt7_2</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>0</v>
-      </c>
-      <c r="F121" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
-      </c>
-      <c r="H121" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>it7A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>IT703_A_b3</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>lt7_2</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
-        <v>0</v>
-      </c>
-      <c r="F122" t="n">
-        <v>1</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
-      </c>
-      <c r="H122" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>it7A3</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>IT703_B</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>t7_2</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
-        <v>4</v>
-      </c>
-      <c r="F123" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>IT703_B_b1</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>lt7_2</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>lab1</t>
-        </is>
-      </c>
-      <c r="H124" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>it7B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>IT703_B_b2</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>lt7_2</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>0</v>
-      </c>
-      <c r="F125" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>lab2</t>
-        </is>
-      </c>
-      <c r="H125" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>it7B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>IT703_B_b3</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>lt7_2</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>lab3</t>
-        </is>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>it7B3</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>IT703_C</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>t7_2</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>4</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>IT703_C_b1</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>lt7_2</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>it7C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>IT703_C_b2</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>lt7_2</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>it7C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>IT703_C_b3</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>IT703</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>lt7_2</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" t="n">
-        <v>1</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>it7C3</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>IT704_A</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>IT704</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>t7_3</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
-        <v>4</v>
-      </c>
-      <c r="F131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>IT704_B</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>IT704</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>t7_3</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>4</v>
-      </c>
-      <c r="F132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>IT704_C</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>IT704</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>t7_3</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>4</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>IT705_A</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>t7_4</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>3</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>IT705_A_b1</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>lt7_4</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>it7A1</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>IT705_A_b2</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>lt7_4</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
-        <v>0</v>
-      </c>
-      <c r="F136" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>it7A2</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>IT705_A_b3</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>lt7_4</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
-        <v>0</v>
-      </c>
-      <c r="F137" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>it7A3</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>IT705_B</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>t7_4</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
-        <v>3</v>
-      </c>
-      <c r="F138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>IT705_B_b1</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>lt7_4</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>lab1</t>
-        </is>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>it7B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>IT705_B_b2</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>lt7_4</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>0</v>
-      </c>
-      <c r="F140" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>lab2</t>
-        </is>
-      </c>
-      <c r="H140" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>it7B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>IT705_B_b3</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>lt7_4</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>0</v>
-      </c>
-      <c r="F141" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>lab3</t>
-        </is>
-      </c>
-      <c r="H141" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>it7B3</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>IT705_C</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>t7_4</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>3</v>
-      </c>
-      <c r="F142" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>IT705_C_b1</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>lt7_4</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>0</v>
-      </c>
-      <c r="F143" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>lab4</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>it7C1</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>IT705_C_b2</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>lt7_4</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" t="n">
-        <v>1</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>lab5</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>it7C2</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>IT705_C_b3</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>IT705</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>lt7_4</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" t="n">
-        <v>1</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>lab6</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>it7C3</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>IT706_A</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>IT706</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>t7_5</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>3</v>
-      </c>
-      <c r="F146" t="n">
-        <v>0</v>
-      </c>
-      <c r="H146" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>IT706_B</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>IT706</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>t7_5</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>3</v>
-      </c>
-      <c r="F147" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>IT706_C</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>IT706</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>t7_5</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>3</v>
-      </c>
-      <c r="F148" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>ITE701_A</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>ITE701</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>t7_6</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>2</v>
-      </c>
-      <c r="F149" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>ITE701_B</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>ITE701</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>t7_6</t>
-        </is>
-      </c>
-      <c r="E150" t="n">
-        <v>2</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0</v>
-      </c>
-      <c r="H150" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>ITE701_C</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>ITE701</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>t7_6</t>
-        </is>
-      </c>
-      <c r="E151" t="n">
-        <v>2</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>ITE702_A</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>it7A</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>ITE702</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>t7_7</t>
-        </is>
-      </c>
-      <c r="E152" t="n">
-        <v>2</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>ITE702_B</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>it7B</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>ITE702</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>t7_7</t>
-        </is>
-      </c>
-      <c r="E153" t="n">
-        <v>2</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>ITE702_C</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>it7C</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>ITE702</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>t7_7</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>2</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10071,7 +8277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10173,19 +8379,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lecture_slots</t>
+          <t>synchronized_batch_labs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>lab_slots</t>
+          <t>classroom_run_length</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10197,10 +8403,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>lecture_slots</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>lab_slots</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>project_slots</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>4</t>
         </is>

--- a/sample_data/it_presentation.xlsx
+++ b/sample_data/it_presentation.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dr. Anjali Deshmukh</t>
+          <t>Dr.Vidya Kubde</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -595,7 +595,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prof. Rahul Patil</t>
+          <t>Dr.R. V. Bhaskarwar</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prof. Aniket Joshi</t>
+          <t>Mrs. A. D. Mhatre</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -687,7 +687,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prof. Sneha Joshi</t>
+          <t>Mrs. G.M.Arwindekar</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -733,7 +733,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Prof. Riya Kulkarni</t>
+          <t>Mr.J. R. Gaidhane</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Prof. Amit Shah</t>
+          <t>Dr. R.A.Jolhe</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -825,7 +825,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Prof. Pooja Kulkarni</t>
+          <t>Ms. D. P. Kadam</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Prof. Sahil Desai</t>
+          <t>Mr. S. U. Kumane</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -917,7 +917,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prof. Vikram More</t>
+          <t>Mrs. K. P. Rane</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -963,7 +963,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prof. Sanika Rane</t>
+          <t>Mrs. H. A.Khot</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prof. Omkar Kale</t>
+          <t>Mrs. A. R. Rahude</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dr. Meera Nair</t>
+          <t>Mrs. N.Y. Moharkar</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Prof. Sandeep Jadhav</t>
+          <t>Mrs. J. S. Phonde</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Prof. Kunal Patil</t>
+          <t>Mr. Krushna Jadhav</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Prof. Neha Desai</t>
+          <t>Mrs. Angel Bency</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Prof. Neelam Shah</t>
+          <t>Mrs. Karishma Shelar</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Prof. Kiran Rao</t>
+          <t>Mrs. Vaishali Korade</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dr. Priya Menon</t>
+          <t>Pallavi M.N.</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Prof. Varun Nair</t>
+          <t>Bipasha</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Prof. Aditya Gokhale</t>
+          <t>Priya Jadhav</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dr. Snehal Shinde</t>
+          <t>Pankaj Rathod</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Prof. Akash Pawar</t>
+          <t>Harshali Vihire</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dr. Shreya Kulkarni</t>
+          <t>Reshma</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Prof. Nikhil Sawant</t>
+          <t>Sample Professor 01</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Prof. Tanvi Rao</t>
+          <t>Sample Professor 02</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Prof. Kavita Iyer</t>
+          <t>Sample Professor 03</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Prof. Pranav More</t>
+          <t>Sample Professor 04</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Prof. Rohit Bhosale</t>
+          <t>Sample Professor 05</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dr. Aditi Naik</t>
+          <t>Sample Professor 06</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Prof. Rohini Jadhav</t>
+          <t>Sample Professor 07</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Prof. Sameer Pawar</t>
+          <t>Sample Professor 08</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Prof. Rutuja More</t>
+          <t>Sample Professor 09</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dr. Harsh Mehta</t>
+          <t>Sample Professor 10</t>
         </is>
       </c>
       <c r="C34" t="n">
